--- a/TTD_051425_formatted.xlsx
+++ b/TTD_051425_formatted.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{7E8413CB-3990-D540-9D14-1CA433DC9CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9A1B1F1-109F-274F-B468-7A3C5FBA85A6}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="7020" windowWidth="34200" windowHeight="19680" xr2:uid="{A18FB856-4BDA-2449-A9D9-3D4BC3E8194B}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19680" xr2:uid="{A18FB856-4BDA-2449-A9D9-3D4BC3E8194B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
